--- a/artfynd/A 53877-2025 artfynd.xlsx
+++ b/artfynd/A 53877-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74933371</v>
+        <v>7120157</v>
       </c>
       <c r="B2" t="n">
-        <v>98248</v>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219606</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pilblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sagittaria sagittifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Domra södra gdn 400 m V, Sm</t>
+          <t>Mosshult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565635</v>
+        <v>565560</v>
       </c>
       <c r="R2" t="n">
-        <v>6437706</v>
+        <v>6437727</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1992-01-01</t>
+          <t>2011-11-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1992-12-31</t>
+          <t>2011-11-01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G7d 4131. SOM: Sagittaria sagittifolia. LEG: Birger Danielsson</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;32791</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,24 +765,625 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Bäck</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>63181407</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56814</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tyllinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>565674</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6438012</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2011-07-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2011-07-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>63189290</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tyllinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>565713</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6437933</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2011-07-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2011-07-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>lokal-ID: C</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>63189306</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tyllinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>565674</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6438012</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2011-07-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2011-07-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>lokal-ID: 13  Box-ID: 13H</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>63228751</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tyllinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>565713</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6437933</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2011-07-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2011-07-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>lokal-ID: C</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>74933371</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98695</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219606</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pilblad</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sagittaria sagittifolia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Domra södra gdn 400 m V, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>565635</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6437706</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1992-12-31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7G7d 4131. SOM: Sagittaria sagittifolia. LEG: Birger Danielsson</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Bäck</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>
